--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2176,6 +2176,127 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122120423</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104494</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>529</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Praktnejlika</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dianthus superbus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vuonoviken, O om, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>912969</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7329920</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Haparanda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nedertorneå</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>BD-Hap-0193</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2003-08-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2003-08-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>"Öster om Vuonoviken, Obskoord: 7327145/1876617/25 m (). I vägkant</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>122120423</v>
       </c>
       <c r="B14" t="n">
-        <v>104494</v>
+        <v>104503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>122120423</v>
       </c>
       <c r="B14" t="n">
-        <v>104503</v>
+        <v>104511</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>122120423</v>
       </c>
       <c r="B14" t="n">
-        <v>104511</v>
+        <v>104513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>122120423</v>
       </c>
       <c r="B14" t="n">
-        <v>104529</v>
+        <v>104539</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>122120423</v>
       </c>
       <c r="B14" t="n">
-        <v>104539</v>
+        <v>104552</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>122120423</v>
       </c>
       <c r="B14" t="n">
-        <v>104552</v>
+        <v>104557</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>122120423</v>
       </c>
       <c r="B14" t="n">
-        <v>104557</v>
+        <v>104566</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2195,11 +2195,6 @@
       </c>
       <c r="E14" t="n">
         <v>529</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Praktnejlika</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>122120423</v>
       </c>
       <c r="B14" t="n">
-        <v>104566</v>
+        <v>104579</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2195,6 +2195,11 @@
       </c>
       <c r="E14" t="n">
         <v>529</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Praktnejlika</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2297,6 +2297,126 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123733521</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104802</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1062</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ryssnarv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Moehringia lateriflora</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Fenzl</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vuono (1), Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>912946</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7329924</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Haparanda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nedertorneå</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>BD-Hap-0010-biogeo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2001-07-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2001-07-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Vuono,, Obskoord: 7327142/1876608/10 m (Avst fr FV-lokal: 16 m).</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mora Aronsson, Tiina Laantee, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -2299,10 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123733521</v>
+        <v>123733525</v>
       </c>
       <c r="B15" t="n">
-        <v>104802</v>
+        <v>104820</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2332,8 +2332,17 @@
           <t>(L.) Fenzl</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2377,17 +2386,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2001-07-18</t>
+          <t>2009-07-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2001-07-18</t>
+          <t>2009-07-18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Vuono,, Obskoord: 7327142/1876608/10 m (Avst fr FV-lokal: 16 m).</t>
+          <t>Vuono, Obskoord: 7327142/1876610/10 m (Avst fr FV-lokal: 17 m). ett blommande ex.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2400,6 +2409,11 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>skogsdunge.</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2408,7 +2422,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mora Aronsson, Tiina Laantee, Thomas Strid</t>
+          <t>Charlotte Wigermo, Erik Ljungstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 3832-2022 artfynd.xlsx
+++ b/artfynd/A 3832-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2176,261 +2176,6 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>122120423</v>
-      </c>
-      <c r="B14" t="n">
-        <v>104579</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>529</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Praktnejlika</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Dianthus superbus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Vuonoviken, O om, Nb</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>912969</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7329920</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Haparanda</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Nedertorneå</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>BD-Hap-0193</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2003-08-17</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2003-08-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>"Öster om Vuonoviken, Obskoord: 7327145/1876617/25 m (). I vägkant</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Ulf Gärdenfors</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>123733525</v>
-      </c>
-      <c r="B15" t="n">
-        <v>104820</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1062</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ryssnarv</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Moehringia lateriflora</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Fenzl</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Vuono (1), Nb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>912946</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7329924</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Haparanda</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Nedertorneå</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>BD-Hap-0010-biogeo</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2009-07-18</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2009-07-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Vuono, Obskoord: 7327142/1876610/10 m (Avst fr FV-lokal: 17 m). ett blommande ex.</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>skogsdunge.</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo, Erik Ljungstrand</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
